--- a/data/trans_camb/P32-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P32-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 7,7</t>
+          <t>1,17; 7,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 8,37</t>
+          <t>1,64; 8,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,47</t>
+          <t>1,17; 7,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 7,81</t>
+          <t>-0,76; 8,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 8,98</t>
+          <t>0,27; 8,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 6,03</t>
+          <t>0,03; 6,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 6,32</t>
+          <t>1,31; 6,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,94</t>
+          <t>1,78; 6,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 6,07</t>
+          <t>1,37; 5,95</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,36; 1496,15</t>
+          <t>23,7; 1749,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,99; 1828,93</t>
+          <t>19,87; 1609,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,98; 1456,77</t>
+          <t>15,15; 1375,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,29; 1077,98</t>
+          <t>33,04; 1344,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47,95; 1122,23</t>
+          <t>42,12; 1318,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,6; 1211,14</t>
+          <t>41,39; 1110,02</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 8,21</t>
+          <t>0,76; 8,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 6,33</t>
+          <t>-0,07; 6,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 4,93</t>
+          <t>-1,39; 4,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 7,13</t>
+          <t>-0,92; 7,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 6,13</t>
+          <t>-0,29; 6,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 6,14</t>
+          <t>-0,83; 6,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 6,76</t>
+          <t>1,02; 6,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,37</t>
+          <t>0,65; 5,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 4,41</t>
+          <t>-0,08; 4,38</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 1443,79</t>
+          <t>5,88; 1361,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-34,06; 1006,38</t>
+          <t>-24,48; 1050,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-46,54; 714,11</t>
+          <t>-60,5; 764,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-69,74; —</t>
+          <t>-54,21; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-47,77; —</t>
+          <t>-66,6; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,01; 891,7</t>
+          <t>20,15; 1042,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,68; 731,86</t>
+          <t>16,89; 725,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 573,12</t>
+          <t>-11,8; 565,45</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 5,47</t>
+          <t>-0,74; 5,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 3,25</t>
+          <t>-2,51; 3,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 7,76</t>
+          <t>-0,26; 7,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 4,72</t>
+          <t>-4,43; 4,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 12,65</t>
+          <t>-1,88; 13,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 3,69</t>
+          <t>-5,55; 3,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 4,66</t>
+          <t>-0,75; 4,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 3,45</t>
+          <t>-1,95; 3,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 6,0</t>
+          <t>-0,19; 6,61</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-23,12; 259,95</t>
+          <t>-23,3; 272,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-58,37; 165,35</t>
+          <t>-56,22; 180,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 374,7</t>
+          <t>-15,15; 353,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-21,41; 231,2</t>
+          <t>-23,38; 260,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-42,71; 187,39</t>
+          <t>-46,45; 190,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 306,96</t>
+          <t>-12,89; 334,64</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 6,83</t>
+          <t>2,17; 7,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 4,37</t>
+          <t>-0,15; 4,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 6,1</t>
+          <t>0,31; 6,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 2,13</t>
+          <t>-2,55; 2,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 3,08</t>
+          <t>-1,79; 3,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 1,48</t>
+          <t>-3,16; 1,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,01</t>
+          <t>1,21; 5,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 3,49</t>
+          <t>-0,17; 3,58</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 3,53</t>
+          <t>-1,5; 3,34</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>42,09; 322,91</t>
+          <t>42,36; 318,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 203,64</t>
+          <t>-7,04; 192,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,62; 267,05</t>
+          <t>1,53; 289,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-72,32; —</t>
+          <t>-81,95; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,93; 244,44</t>
+          <t>29,64; 280,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 195,76</t>
+          <t>-7,39; 192,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-42,51; 163,87</t>
+          <t>-44,34; 165,8</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 5,56</t>
+          <t>-1,44; 5,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 6,39</t>
+          <t>-1,35; 6,34</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,3; 10,2</t>
+          <t>1,34; 9,91</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 1,76</t>
+          <t>-6,64; 1,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,69; -0,24</t>
+          <t>-8,38; -0,06</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 3,12</t>
+          <t>-6,01; 3,53</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 3,16</t>
+          <t>-2,03; 3,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 3,06</t>
+          <t>-2,05; 3,35</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,12; 6,42</t>
+          <t>0,48; 6,49</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-34,42; 561,13</t>
+          <t>-40,16; 505,71</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-30,74; 573,43</t>
+          <t>-39,71; 538,99</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2,99; 1090,73</t>
+          <t>7,0; 912,27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-90,51; 156,84</t>
+          <t>-90,84; 170,08</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 70,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-77,53; 193,64</t>
+          <t>-76,15; 269,86</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-46,8; 190,88</t>
+          <t>-45,06; 177,93</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-50,69; 157,84</t>
+          <t>-44,75; 204,09</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 337,3</t>
+          <t>3,15; 352,48</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>4,21; 17,01</t>
+          <t>3,7; 18,1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 10,82</t>
+          <t>-0,36; 10,99</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 22,95</t>
+          <t>-2,69; 21,8</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 2,91</t>
+          <t>-0,52; 2,87</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,49; 7,13</t>
+          <t>1,48; 6,99</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 8,89</t>
+          <t>-0,85; 8,73</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,66; 6,99</t>
+          <t>1,56; 6,87</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,73; 6,99</t>
+          <t>1,47; 7,14</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 10,63</t>
+          <t>-0,32; 11,15</t>
         </is>
       </c>
     </row>
@@ -1863,17 +1863,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>44,14; 853,21</t>
+          <t>39,0; 876,92</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-22,64; 596,34</t>
+          <t>-17,86; 610,24</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1297,91</t>
+          <t>-67,27; 1514,68</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>49,12; 906,19</t>
+          <t>35,45; 736,77</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>38,79; 838,19</t>
+          <t>31,13; 685,01</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-50,7; 1094,78</t>
+          <t>-41,75; 1295,03</t>
         </is>
       </c>
     </row>
@@ -1973,32 +1973,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,35</t>
+          <t>2,57; 5,4</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,84</t>
+          <t>1,21; 3,91</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,13</t>
+          <t>2,11; 5,25</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,98</t>
+          <t>-0,64; 1,95</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,07</t>
+          <t>0,35; 3,08</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,03</t>
+          <t>-1,1; 1,93</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -2008,12 +2008,12 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,2</t>
+          <t>1,22; 3,18</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,43</t>
+          <t>0,9; 3,47</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>81,4; 240,96</t>
+          <t>77,53; 243,55</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>39,4; 167,72</t>
+          <t>33,44; 168,98</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>56,14; 223,4</t>
+          <t>60,49; 220,1</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-33,64; 201,45</t>
+          <t>-33,54; 208,72</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>11,12; 328,41</t>
+          <t>15,75; 375,62</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-45,33; 211,55</t>
+          <t>-49,87; 207,9</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>67,72; 202,72</t>
+          <t>64,74; 197,27</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>48,94; 173,2</t>
+          <t>42,52; 169,78</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>34,58; 173,63</t>
+          <t>35,73; 172,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P32-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P32-Clase-trans_camb.xlsx
@@ -634,37 +634,37 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>4,61</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,74</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,74</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,55</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4,2</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,5</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,74</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,39</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,55</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4,2</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,5</t>
+          <t>3,88</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 7,76</t>
+          <t>1,33; 7,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 8,43</t>
+          <t>1,34; 8,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 7,86</t>
+          <t>1,6; 8,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 8,29</t>
+          <t>-0,76; 7,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 8,1</t>
+          <t>0,31; 8,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 6,1</t>
+          <t>-0,03; 6,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,65</t>
+          <t>1,22; 6,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 6,97</t>
+          <t>1,85; 6,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 5,95</t>
+          <t>1,44; 6,07</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>275,62%</t>
+          <t>302,57%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>309,99%</t>
+          <t>354,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>270,21%</t>
+          <t>299,99%</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,7; 1749,09</t>
+          <t>18,66; 1347,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,87; 1609,32</t>
+          <t>23,0; 1267,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,15; 1375,85</t>
+          <t>14,04; 1202,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,04; 1344,88</t>
+          <t>42,31; 1400,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>42,12; 1318,38</t>
+          <t>45,59; 1282,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>41,39; 1110,02</t>
+          <t>27,03; 1135,36</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>2,18</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>3,11</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,06</t>
+          <t>2,56</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 8,19</t>
+          <t>0,53; 8,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 6,28</t>
+          <t>-0,33; 6,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 4,8</t>
+          <t>-0,54; 5,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 7,04</t>
+          <t>-1,16; 6,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 6,42</t>
+          <t>-0,42; 6,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 6,02</t>
+          <t>-0,16; 6,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 6,77</t>
+          <t>0,97; 6,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,08</t>
+          <t>0,45; 5,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 4,38</t>
+          <t>0,23; 4,97</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>102,36%</t>
+          <t>121,2%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>184,71%</t>
+          <t>243,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>129,43%</t>
+          <t>160,9%</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,88; 1361,87</t>
+          <t>-17,69; 1254,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-24,48; 1050,1</t>
+          <t>-21,1; 1042,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-60,5; 764,33</t>
+          <t>-39,49; 1019,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,21; —</t>
+          <t>-62,87; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,6; —</t>
+          <t>-41,42; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,15; 1042,96</t>
+          <t>8,85; 752,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,89; 725,58</t>
+          <t>-1,24; 663,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-11,8; 565,45</t>
+          <t>-7,25; 653,57</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,26</t>
+          <t>3,66</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,06</t>
+          <t>-0,12</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,72</t>
+          <t>3,0</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 5,52</t>
+          <t>-0,81; 5,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 3,04</t>
+          <t>-2,55; 3,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 7,69</t>
+          <t>-0,0; 8,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 4,82</t>
+          <t>-5,05; 4,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 13,55</t>
+          <t>-1,88; 11,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 3,87</t>
+          <t>-5,58; 3,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 4,87</t>
+          <t>-0,54; 5,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 3,56</t>
+          <t>-1,84; 3,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 6,61</t>
+          <t>-0,14; 6,73</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>111,54%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-3,23%</t>
+          <t>-6,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-23,3; 272,49</t>
+          <t>-23,72; 266,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-56,22; 180,25</t>
+          <t>-56,09; 175,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 353,4</t>
+          <t>-3,97; 405,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-23,38; 260,11</t>
+          <t>-15,88; 263,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-46,45; 190,22</t>
+          <t>-47,58; 196,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-12,89; 334,64</t>
+          <t>-10,86; 331,04</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,89</t>
+          <t>2,8</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,4</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>2,19</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,12</t>
+          <t>2,07; 6,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 4,42</t>
+          <t>-0,1; 4,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 6,21</t>
+          <t>0,46; 5,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 2,11</t>
+          <t>-2,88; 1,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 3,16</t>
+          <t>-1,57; 3,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 1,49</t>
+          <t>-1,47; 4,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 5,23</t>
+          <t>1,29; 5,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 3,58</t>
+          <t>-0,11; 3,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 3,34</t>
+          <t>0,32; 4,48</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-32,23%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>81,89%</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>42,36; 318,95</t>
+          <t>47,58; 314,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 192,04</t>
+          <t>-7,9; 212,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,53; 289,61</t>
+          <t>9,93; 272,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-81,95; —</t>
+          <t>-81,67; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,64; 280,64</t>
+          <t>31,87; 261,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 192,95</t>
+          <t>-7,52; 159,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-44,34; 165,8</t>
+          <t>4,28; 222,91</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5,5</t>
+          <t>6,38</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,55</t>
+          <t>-0,86</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,26</t>
+          <t>3,65</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 5,33</t>
+          <t>-1,81; 5,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 6,34</t>
+          <t>-0,83; 6,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,34; 9,91</t>
+          <t>2,02; 11,09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 1,96</t>
+          <t>-6,74; 1,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,38; -0,06</t>
+          <t>-7,68; 0,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 3,53</t>
+          <t>-5,8; 2,68</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 3,16</t>
+          <t>-2,28; 3,46</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 3,35</t>
+          <t>-2,65; 3,04</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,48; 6,49</t>
+          <t>0,31; 6,83</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>208,29%</t>
+          <t>241,64%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-13,27%</t>
+          <t>-20,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>101,19%</t>
+          <t>113,09%</t>
         </is>
       </c>
     </row>
@@ -1647,22 +1647,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-40,16; 505,71</t>
+          <t>-49,34; 500,34</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-39,71; 538,99</t>
+          <t>-33,12; 520,16</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7,0; 912,27</t>
+          <t>29,34; 1082,18</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-90,84; 170,08</t>
+          <t>-90,75; 158,91</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1672,29 +1672,29 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-76,15; 269,86</t>
+          <t>-75,42; 213,26</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-45,06; 177,93</t>
+          <t>-45,26; 189,06</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-44,75; 204,09</t>
+          <t>-53,33; 162,08</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3,15; 352,48</t>
+          <t>-6,44; 408,41</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5,29</t>
+          <t>5,31</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>1,33</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3,28</t>
+          <t>2,98</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>3,7; 18,1</t>
+          <t>4,42; 17,91</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 10,99</t>
+          <t>-1,04; 10,6</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 21,8</t>
+          <t>-2,56; 20,01</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 2,87</t>
+          <t>-0,28; 3,02</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,99</t>
+          <t>1,69; 7,32</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 8,73</t>
+          <t>-0,85; 8,63</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,56; 6,87</t>
+          <t>1,4; 6,86</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,47; 7,14</t>
+          <t>1,53; 6,97</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 11,15</t>
+          <t>-0,89; 9,3</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>134,12%</t>
+          <t>134,42%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>325,15%</t>
+          <t>307,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>181,37%</t>
+          <t>165,05%</t>
         </is>
       </c>
     </row>
@@ -1863,17 +1863,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>39,0; 876,92</t>
+          <t>51,83; 971,01</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-17,86; 610,24</t>
+          <t>-23,02; 590,63</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-67,27; 1514,68</t>
+          <t>-100,0; 1357,13</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>35,45; 736,77</t>
+          <t>35,43; 734,57</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>31,13; 685,01</t>
+          <t>43,68; 757,29</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-41,75; 1295,03</t>
+          <t>-57,96; 954,93</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3,47</t>
+          <t>3,75</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>1,51</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,26</t>
+          <t>2,94</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,57; 5,4</t>
+          <t>2,73; 5,43</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,91</t>
+          <t>1,4; 3,82</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,25</t>
+          <t>2,34; 5,52</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,95</t>
+          <t>-0,47; 2,15</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,08</t>
+          <t>0,46; 3,07</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 1,93</t>
+          <t>0,13; 2,93</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,88</t>
+          <t>1,92; 3,96</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,18</t>
+          <t>1,23; 3,34</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,47</t>
+          <t>1,9; 4,19</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>126,56%</t>
+          <t>136,56%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>102,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>125,79%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>77,53; 243,55</t>
+          <t>80,83; 245,95</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>33,44; 168,98</t>
+          <t>41,19; 186,23</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>60,49; 220,1</t>
+          <t>69,15; 255,04</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-33,54; 208,72</t>
+          <t>-30,66; 240,44</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>15,75; 375,62</t>
+          <t>18,58; 343,94</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-49,87; 207,9</t>
+          <t>0,43; 297,88</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>64,74; 197,27</t>
+          <t>67,51; 208,65</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>42,52; 169,78</t>
+          <t>43,03; 174,93</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>35,73; 172,72</t>
+          <t>65,31; 211,01</t>
         </is>
       </c>
     </row>
